--- a/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 16,81</t>
+          <t>-2,87; 18,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 11,36</t>
+          <t>-5,57; 10,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 5,06</t>
+          <t>-17,17; 5,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 0,0</t>
+          <t>-22,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 8,52</t>
+          <t>-6,33; 8,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 2,96</t>
+          <t>-8,97; 3,95</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,72</t>
+          <t>-5,39; 1,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,5</t>
+          <t>-5,66; 0,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,45</t>
+          <t>-4,58; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,31</t>
+          <t>-4,73; 1,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,62</t>
+          <t>-3,39; 0,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,44</t>
+          <t>-3,34; 0,44</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 141,41</t>
+          <t>-100,0; 183,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,44</t>
+          <t>-100,0; 163,7</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,06</t>
+          <t>-2,84; 2,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,64</t>
+          <t>-3,56; 0,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,32</t>
+          <t>-3,68; 1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,27</t>
+          <t>-3,42; 1,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,07</t>
+          <t>-2,21; 1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,53</t>
+          <t>-2,69; 0,53</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,35; 215,66</t>
+          <t>-90,23; 223,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 304,23</t>
+          <t>-89,83; 428,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,11; 117,56</t>
+          <t>-73,54; 131,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,59; 69,8</t>
+          <t>-88,32; 85,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 18,77</t>
+          <t>-2,96; 17,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 10,57</t>
+          <t>-5,49; 13,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 5,02</t>
+          <t>-16,65; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 0,0</t>
+          <t>-20,66; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 8,55</t>
+          <t>-6,45; 8,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,95</t>
+          <t>-9,41; 4,0</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,64; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 1,09</t>
+          <t>-4,79; 0,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,5</t>
+          <t>-5,26; 0,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,32</t>
+          <t>-4,28; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,73</t>
+          <t>-4,34; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,65</t>
+          <t>-3,26; 0,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,44</t>
+          <t>-3,52; 0,52</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 183,76</t>
+          <t>-100,0; 239,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 163,7</t>
+          <t>-100,0; 152,72</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,8</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,12</t>
+          <t>-2,6; 2,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,87</t>
+          <t>-3,48; 0,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,29</t>
+          <t>-3,7; 1,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,41</t>
+          <t>-3,65; 1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,14</t>
+          <t>-2,36; 1,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,53</t>
+          <t>-2,96; 0,29</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,23; 223,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,83; 428,37</t>
+          <t>-100,0; 203,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 131,28</t>
+          <t>-75,45; 143,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,32; 85,29</t>
+          <t>-90,55; 49,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,97</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,63</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>5,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 17,63</t>
+          <t>-17,81; 5,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 13,05</t>
+          <t>-23,3; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 2,79</t>
+          <t>-2,84; 16,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 0,0</t>
+          <t>-5,61; 11,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 8,86</t>
+          <t>-6,21; 8,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 4,0</t>
+          <t>-9,25; 2,96</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-59,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>207,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>20,68%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-59,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,64; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-1,08</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-1,3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,97</t>
+          <t>-4,55; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,5</t>
+          <t>-4,52; 1,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,56</t>
+          <t>-5,45; 0,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,55</t>
+          <t>-5,64; 0,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,75</t>
+          <t>-3,42; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,52</t>
+          <t>-3,44; 0,44</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-49,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-41,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-60,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-72,37%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-49,18%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-41,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 239,32</t>
+          <t>-100,0; 141,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,72</t>
+          <t>-100,0; 93,44</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,99</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,31</t>
+          <t>-3,64; 1,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,71</t>
+          <t>-3,66; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,24</t>
+          <t>-2,76; 2,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,16</t>
+          <t>-3,7; 0,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,23</t>
+          <t>-2,26; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,29</t>
+          <t>-2,52; 0,53</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-37,93%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-44,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-3,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-56,94%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-37,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-44,06%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,35; 215,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 304,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 203,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 143,0</t>
+          <t>-75,11; 117,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,55; 49,78</t>
+          <t>-88,59; 69,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,275 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,63</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.8366192200790273</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.545858946414424</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.659010979735088</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.3812766108212622</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.4497990546873862</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.6097437657874649</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,81; 5,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-23,3; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 16,81</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,61; 11,36</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-6,21; 8,52</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-9,25; 2,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.957914471636289</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.765906597215934</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.4812516048787616</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.320654812583526</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.400783144455228</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.176407884351005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-59,92%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>207,56%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-57,46%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.389121138860948</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.684068746454201</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.184619501168315</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.414093291968637</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.8118027027064187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-0.5412002317672914</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2.520866133126202</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.5793495686966076</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4119273808860274</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5584052474876341</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 1,45</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 1,31</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 0,72</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,64; 0,5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 0,62</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-3,44; 0,44</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-49,18%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-41,78%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-60,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-72,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-54,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-56,66%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.1215857786410634</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1438986746054279</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.166280834557292</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.2363184421131056</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.1434666793507337</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.1904669336850493</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 141,41</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 93,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.7490045504622728</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.7555563910004865</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.8470304289052134</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.04524353319698</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.5858083483656422</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.6629553098461665</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5394177726270085</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.372719105140599</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3621839261870627</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.1387608043666048</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.2349689787202113</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.1512998696599422</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,03</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,85</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.3099872137801685</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3668747258614878</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.4788663909547352</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6805652605247025</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3864240619640497</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5130181204269827</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>2.813208065482586</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +876,283 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.4227961643017146</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3444009466788789</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.2138508829802616</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.1792723243968652</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,64; 1,32</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,66; 1,27</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,76; 2,06</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,7; 0,64</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 1,07</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 0,53</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-37,93%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-44,06%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-3,31%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-56,94%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-24,22%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-50,66%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.95559773324741</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.733522116246776</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>1.277699245928919</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.8513841436014918</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-89,35; 215,66</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 304,23</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-75,11; 117,56</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-88,59; 69,8</t>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.08984109024735742</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1954464141671616</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1146411118056799</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.1379710597825384</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.009472862987343908</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.1676028703625573</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.615727505541355</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.711696534760924</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.4156063166051061</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.6504713020435777</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.374914163508166</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.5402586733970092</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.4514501511333036</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.2458000414684933</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.7022441453814093</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.1780906555785113</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.3817804920721327</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.1097824781800541</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.2018521266915713</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.4391228361684273</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.3821819214668863</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.4599575484220022</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.02528509341161161</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.4473678378789412</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.8653713583376004</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.6734708369940955</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.8627559178906892</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4.687938938789328</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.103545016373939</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>2.06255590468893</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.8753643548668861</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1160,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
